--- a/analysis/tables/bloom-7b1.xlsx
+++ b/analysis/tables/bloom-7b1.xlsx
@@ -536,27 +536,27 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.004054301607032</v>
+        <v>0.8099371366296725</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2364620828859584</v>
+        <v>-0.1896062154776302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>y = 1.004x - 0.236</t>
+          <t>y = 0.810x - 0.190</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8036599213638229</v>
+        <v>0.8036599213638219</v>
       </c>
       <c r="H3" t="n">
         <v>0.08309191886343829</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2355072654013738</v>
+        <v>0.2340999157868272</v>
       </c>
       <c r="J3" t="n">
-        <v>0.767592218721074</v>
+        <v>0.6203309211520422</v>
       </c>
       <c r="K3" t="n">
         <v>0.1660500395743601</v>
@@ -577,27 +577,27 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9823500619064619</v>
+        <v>0.8032294104731906</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1855439549652754</v>
+        <v>-0.1793615301419243</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>y = 0.982x - 0.186</t>
+          <t>y = 0.803x - 0.179</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8139452667649676</v>
+        <v>0.8066501015898672</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08263021887197465</v>
+        <v>0.08295769233715304</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1888776335038727</v>
+        <v>0.2233005014548217</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7968061069411865</v>
+        <v>0.6238678803312663</v>
       </c>
       <c r="K4" t="n">
         <v>0.1660500395743601</v>
